--- a/code/Created Files for Analysis/possible_target_vars.xlsx
+++ b/code/Created Files for Analysis/possible_target_vars.xlsx
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Anzahl Laender</t>
+          <t>Anzahl Länder</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
